--- a/Data/kantonale_vorlagen_list.xlsx
+++ b/Data/kantonale_vorlagen_list.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="106">
   <si>
     <t>Kanton</t>
   </si>
@@ -29,15 +29,27 @@
     <t>Vorlage_i</t>
   </si>
   <si>
+    <t>ZH</t>
+  </si>
+  <si>
+    <t>BE</t>
+  </si>
+  <si>
     <t>LU</t>
   </si>
   <si>
-    <t>UR</t>
+    <t>SZ</t>
+  </si>
+  <si>
+    <t>NW</t>
   </si>
   <si>
     <t>SO</t>
   </si>
   <si>
+    <t>BS</t>
+  </si>
+  <si>
     <t>BL</t>
   </si>
   <si>
@@ -50,157 +62,274 @@
     <t>AG</t>
   </si>
   <si>
+    <t>TG</t>
+  </si>
+  <si>
     <t>TI</t>
   </si>
   <si>
+    <t>VD</t>
+  </si>
+  <si>
+    <t>NE</t>
+  </si>
+  <si>
     <t>GE</t>
   </si>
   <si>
-    <t>303614</t>
-  </si>
-  <si>
-    <t>368095</t>
-  </si>
-  <si>
-    <t>368241</t>
-  </si>
-  <si>
-    <t>364738</t>
-  </si>
-  <si>
-    <t>364739</t>
-  </si>
-  <si>
-    <t>364740</t>
-  </si>
-  <si>
-    <t>364741</t>
-  </si>
-  <si>
-    <t>429185</t>
-  </si>
-  <si>
-    <t>429388</t>
-  </si>
-  <si>
-    <t>429482</t>
-  </si>
-  <si>
-    <t>430618</t>
-  </si>
-  <si>
-    <t>430619</t>
-  </si>
-  <si>
-    <t>430620</t>
-  </si>
-  <si>
-    <t>430636</t>
-  </si>
-  <si>
-    <t>430652</t>
-  </si>
-  <si>
-    <t>430668</t>
-  </si>
-  <si>
-    <t>368987</t>
-  </si>
-  <si>
-    <t>365050</t>
-  </si>
-  <si>
-    <t>365051</t>
-  </si>
-  <si>
-    <t>365052</t>
-  </si>
-  <si>
-    <t>373211</t>
-  </si>
-  <si>
-    <t>373212</t>
-  </si>
-  <si>
-    <t>373704</t>
-  </si>
-  <si>
-    <t>435591</t>
-  </si>
-  <si>
-    <t>Ausbau der Kantonsstrasse K 36 durch die Lammschlucht im Entlebuch, 2. Abschnitt</t>
-  </si>
-  <si>
-    <t>Teilrevision des Energiegesetzes des Kantons Uri (EnG)</t>
-  </si>
-  <si>
-    <t>Kantonale Volksinitiative «Streichung der Abgangsentschädigung für den Urner Regierungsrat (Abschaffung goldener Fallschirm)»</t>
-  </si>
-  <si>
-    <t>Neubau «KAPO-Stützpunkt» in Oensingen; Bewilligung eines Verpflichtungskredites</t>
-  </si>
-  <si>
-    <t>Änderung des Sozialgesetzes (SG); Umsetzung Massnahmenplan 2024 DDI: Finanzierung der erlassenen Mindestbeiträge an die AHV durch die Einwohnergemeinden</t>
-  </si>
-  <si>
-    <t>Änderung des Sozialgesetzes (SG); Umsetzung Massnahmenplan 2024 DDI: Weiterverrechnung der Verwaltungskosten für die Durchführung der Alimentenhilfe an die Einwohnergemeinden</t>
-  </si>
-  <si>
-    <t>Teilrevision des Sozialgesetzes (SG); Anhebung der Familienzulagen</t>
-  </si>
-  <si>
-    <t>Initiative Tempo 30 auf Hauptstrassen</t>
-  </si>
-  <si>
-    <t>Initiative Tempo 30 auf Hauptstrassen: Gegenvorschlag</t>
-  </si>
-  <si>
-    <t>Initiative Tempo 30 auf Hauptstrassen: Stichfrage</t>
-  </si>
-  <si>
-    <t>Initiative Prämienabzug für alle</t>
-  </si>
-  <si>
-    <t>Initiative Prämienabzug für alle: Gegenvorschlag</t>
-  </si>
-  <si>
-    <t>Initiative Prämienabzug für alle: Stichfrage</t>
-  </si>
-  <si>
-    <t>Solar-Initiative</t>
-  </si>
-  <si>
-    <t>Transparenz- und Mitwirkungsinitiative</t>
-  </si>
-  <si>
-    <t>Verfassungsänderung Kreislaufwirtschaft</t>
-  </si>
-  <si>
-    <t>Änderung des Gesetzes über die Förderung des öffentlichen Verkehrs</t>
-  </si>
-  <si>
-    <t>Kantonsratsbeschluss über den Verkauf der Grundstücke WILWEST und die Kompensation von Fruchtfolgeflächen im Kanton St.Gallen</t>
-  </si>
-  <si>
-    <t>Kantonsratsbeschluss über den Neubau des Berufs- und Weiterbildungszentrums Rapperswil-Jona am Standort «Südquartier» in Rapperswil</t>
-  </si>
-  <si>
-    <t>Kantonsratsbeschluss über den Bau der «Kantonsstrasse zum See» mit Kostenbeteiligung am «Anschluss Witen mit Zubringer»</t>
-  </si>
-  <si>
-    <t>Aargauische Volksinitiative "Arbeit muss sich lohnen!" vom 24. April 2024</t>
-  </si>
-  <si>
-    <t>Aargauische Volksinitiative "Blitzerabzocke stoppen!" vom 18. September 2024</t>
+    <t>548599</t>
+  </si>
+  <si>
+    <t>548600</t>
+  </si>
+  <si>
+    <t>548601</t>
+  </si>
+  <si>
+    <t>548602</t>
+  </si>
+  <si>
+    <t>548603</t>
+  </si>
+  <si>
+    <t>548604</t>
+  </si>
+  <si>
+    <t>548605</t>
+  </si>
+  <si>
+    <t>548606</t>
+  </si>
+  <si>
+    <t>548607</t>
+  </si>
+  <si>
+    <t>534886</t>
+  </si>
+  <si>
+    <t>569507</t>
+  </si>
+  <si>
+    <t>569903</t>
+  </si>
+  <si>
+    <t>581510</t>
+  </si>
+  <si>
+    <t>581536</t>
+  </si>
+  <si>
+    <t>581539</t>
+  </si>
+  <si>
+    <t>581542</t>
+  </si>
+  <si>
+    <t>571115</t>
+  </si>
+  <si>
+    <t>571116</t>
+  </si>
+  <si>
+    <t>562134</t>
+  </si>
+  <si>
+    <t>562139</t>
+  </si>
+  <si>
+    <t>562140</t>
+  </si>
+  <si>
+    <t>562143</t>
+  </si>
+  <si>
+    <t>582013</t>
+  </si>
+  <si>
+    <t>582014</t>
+  </si>
+  <si>
+    <t>578370</t>
+  </si>
+  <si>
+    <t>578375</t>
+  </si>
+  <si>
+    <t>578380</t>
+  </si>
+  <si>
+    <t>569515</t>
+  </si>
+  <si>
+    <t>569518</t>
+  </si>
+  <si>
+    <t>551770</t>
+  </si>
+  <si>
+    <t>572340</t>
+  </si>
+  <si>
+    <t>572341</t>
+  </si>
+  <si>
+    <t>569966</t>
+  </si>
+  <si>
+    <t>575768</t>
+  </si>
+  <si>
+    <t>575769</t>
+  </si>
+  <si>
+    <t>578209</t>
+  </si>
+  <si>
+    <t>578218</t>
+  </si>
+  <si>
+    <t>578225</t>
+  </si>
+  <si>
+    <t>578226</t>
+  </si>
+  <si>
+    <t>575408</t>
+  </si>
+  <si>
+    <t>573561</t>
+  </si>
+  <si>
+    <t>573562</t>
+  </si>
+  <si>
+    <t>Verfassung des Kantons Zürich (Änderung vom 15. September 2025; Vertretung von Kantonsratsmitgliedern)</t>
+  </si>
+  <si>
+    <t>Kantonale Volksinitiative «Wohneigentum wieder ermöglichen (Wohneigentums-Initiative)»</t>
+  </si>
+  <si>
+    <t>A. Kantonale Volksinitiative für mehr günstige und gemeinnützige Wohnungen («Wohnungsinitiative»)</t>
+  </si>
+  <si>
+    <t>B. Gegenvorschlag des Kantonsrates vom 17. November 2025</t>
+  </si>
+  <si>
+    <t>C. Stichfrage: Welche der beiden Vorlagen soll in Kraft treten, falls sowohl die kantonale Volksinitiative als auch der Gegenvorschlag des Kantonsrates angenommen werden?</t>
+  </si>
+  <si>
+    <t>A. Kantonale Volksinitiative «Bezahlbare Wohnungen schützen. Leerkündigungen stoppen (Wohnschutz-Initiative)»</t>
+  </si>
+  <si>
+    <t>B. Gegenvorschlag des Kantonsrates</t>
+  </si>
+  <si>
+    <t>Kantonale Volksinitiative «Stopp Prämien-Schock: Für eine automatische Entlastung bei den Krankenkassenprämien»</t>
+  </si>
+  <si>
+    <t>Projektierungskredit für das Kunstmuseum Bern (Sanierung und Ersatzneubau)</t>
+  </si>
+  <si>
+    <t>Neuer Standort Kantonsgericht. Kauf Grundstück Würzenbachstrasse 8, Luzern</t>
+  </si>
+  <si>
+    <t>Volksinitiative «Kaufkraft stärken – Prämienverbilligung auch für den Mittelstand»</t>
+  </si>
+  <si>
+    <t>Bewilligung eines Objektkredits für den Ersatzneubau einer Dreifachsporthalle für die kantonale Mittelschule</t>
+  </si>
+  <si>
+    <t>Vorlage des Landrates - Teilrevision des Gesetzes über die Steuern des Kantons und der Gemeinden (Steuergesetz, StG)</t>
+  </si>
+  <si>
+    <t>Gegenvorschlag Referendumskomitee - Teilrevision des Gesetzes über die Steuern des Kantons und der Gemeinden (Steuergesetz, StG)</t>
+  </si>
+  <si>
+    <t>Stichfrage</t>
+  </si>
+  <si>
+    <t>Stellvertretung im Kantonsrat bei Mutterschaft: Änderung der Kantonsverfassung</t>
+  </si>
+  <si>
+    <t>Stellvertretung im Kantonsrat bei Mutterschaft: Änderung des Kantonsratsgesetzes</t>
+  </si>
+  <si>
+    <t>Grossratsbeschluss vom 22. Oktober 2025 betreffend Änderung des Gesetzes über die direkten Steuern (Steuergesetz, StG)</t>
+  </si>
+  <si>
+    <t>Kantonale Initiative für ein «Neues Stadttaubenkonzept Kanton Basel-Stadt»</t>
+  </si>
+  <si>
+    <t>Grossratsbeschluss vom 7. Januar 2026 betreffend Finanzierung der weiteren Arbeit im Zusammenhang mit dem Herzstück und dem Bahnknoten Basel</t>
+  </si>
+  <si>
+    <t>Kantonale Initiative «Für die Wiederherstellung und Wiederaufforstung der ehemaligen Klybeckinsel (Klybeckinsel-Volksinitiative)»</t>
+  </si>
+  <si>
+    <t>Gegenvorschlag des Grossen Rates vom 7. Januar 2026</t>
+  </si>
+  <si>
+    <t>Stichfrage zu Initiative und Gegenvorschlag</t>
+  </si>
+  <si>
+    <t>Verfassungsinitiative Zämme in Europa</t>
+  </si>
+  <si>
+    <t>Gesetzesinitiative Energiepolitik nur mit der Bevölkerung</t>
+  </si>
+  <si>
+    <t>Neue Ortsdurchfahrt Birsfelden</t>
+  </si>
+  <si>
+    <t>Teilrevision der Verfassung des Kantons Schaffhausen (Finanzrechtliche Befugnisse)</t>
+  </si>
+  <si>
+    <t>Verpflichtungskredit für das Sportinfrastrukturprojekt «Erweiterung Hallensportzentrum Schweizersbild»</t>
+  </si>
+  <si>
+    <t>Gesetz über Beiträge für familien- und schulergänzende Kinderbetreuung</t>
+  </si>
+  <si>
+    <t>Verkehrsinfrastruktur-Entwicklung Raum Suhr (VERAS); Verpflichtungskredit vom 16. Dezember 2025</t>
+  </si>
+  <si>
+    <t>Aargauische Volksinitiative "Bildungsqualität sichern – JETZT!" vom 28. August 2024</t>
+  </si>
+  <si>
+    <t>Änderung der Kantonsverfassung zur Anpassung der Finanzkompetenzen</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>Loi modifiant la loi sur l'inspection et les relations du travail (LIRT)</t>
-  </si>
-  <si>
-    <t>Iniziativa popolare legislativa generica "Rispetto per i diritti di chi lavora! Combattiamo il dumping salariale!"</t>
+    <t>Crédit d’étude pour le Musée des Beaux-Arts de Berne (rénovation et construction d’un bâtiment de remplacement)</t>
+  </si>
+  <si>
+    <t>Initiative populaire constitutionnelle « Pour le droit de vivre dignement de son travail – pour un salaire minimum cantonal »</t>
+  </si>
+  <si>
+    <t>Initiative populaire législative « Pour le droit de vivre dignement de son travail – pour un salaire minimum cantonal »</t>
+  </si>
+  <si>
+    <t>Contre-projet législatif « Loi sur le salaire minimum »</t>
+  </si>
+  <si>
+    <t>Question subsidiaire</t>
+  </si>
+  <si>
+    <t>Décret du 17 février 2026 modifiant la Constitution de la République et Canton de Neuchâtel (Cst. NE) (Pour la reconnaissance des aînées et des aînés dans la Constitution)</t>
+  </si>
+  <si>
+    <t>Loi pour une expression non ostentatoire des convictions religieuses</t>
+  </si>
+  <si>
+    <t>Loi sur les heures d'ouverture des magasins (LHOM) (Ouverture du dimanche)</t>
+  </si>
+  <si>
+    <t>Iniziativa popolare legislativa generica "Per il rimborso delle cure dentarie"</t>
+  </si>
+  <si>
+    <t>Iniziativa popolare costituzionale elaborata "Si alla neutralizzazione dell'aumento dei valori di stima"</t>
   </si>
 </sst>
 </file>
@@ -270,186 +399,186 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="D2" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="E2" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="D3" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="E3" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="D4" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="E4" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="D5" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="E5" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="D6" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="E6" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="D7" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="E7" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="D8" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="E8" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="D9" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="E9" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="D10" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="E10" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="D11" t="s">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="E11" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="D12" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="E12" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -457,101 +586,101 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="D13" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="E13" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="D14" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="E14" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="D15" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="E15" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="D16" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="E16" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B17" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="D17" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="E17" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="D18" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="E18" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19">
@@ -559,50 +688,50 @@
         <v>10</v>
       </c>
       <c r="B19" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="D19" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="E19" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="D20" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="E20" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C21" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="D21" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="E21" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="22">
@@ -610,16 +739,16 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C22" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="D22" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="E22" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23">
@@ -627,50 +756,356 @@
         <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C23" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="D23" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="E23" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C24" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="D24" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="E24" t="s">
-        <v>62</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25" t="s">
+        <v>85</v>
+      </c>
+      <c r="D25" t="s">
+        <v>95</v>
+      </c>
+      <c r="E25" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>12</v>
+      </c>
+      <c r="B26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" t="s">
+        <v>86</v>
+      </c>
+      <c r="D26" t="s">
+        <v>95</v>
+      </c>
+      <c r="E26" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>12</v>
+      </c>
+      <c r="B27" t="s">
+        <v>46</v>
+      </c>
+      <c r="C27" t="s">
+        <v>87</v>
+      </c>
+      <c r="D27" t="s">
+        <v>95</v>
+      </c>
+      <c r="E27" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" t="s">
+        <v>47</v>
+      </c>
+      <c r="C28" t="s">
+        <v>88</v>
+      </c>
+      <c r="D28" t="s">
+        <v>95</v>
+      </c>
+      <c r="E28" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
         <v>13</v>
       </c>
-      <c r="B25" t="s">
-        <v>37</v>
-      </c>
-      <c r="C25" t="s">
+      <c r="B29" t="s">
+        <v>48</v>
+      </c>
+      <c r="C29" t="s">
+        <v>89</v>
+      </c>
+      <c r="D29" t="s">
+        <v>95</v>
+      </c>
+      <c r="E29" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>13</v>
+      </c>
+      <c r="B30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C30" t="s">
+        <v>90</v>
+      </c>
+      <c r="D30" t="s">
+        <v>95</v>
+      </c>
+      <c r="E30" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>14</v>
+      </c>
+      <c r="B31" t="s">
+        <v>50</v>
+      </c>
+      <c r="C31" t="s">
+        <v>91</v>
+      </c>
+      <c r="D31" t="s">
+        <v>95</v>
+      </c>
+      <c r="E31" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" t="s">
+        <v>51</v>
+      </c>
+      <c r="C32" t="s">
+        <v>92</v>
+      </c>
+      <c r="D32" t="s">
+        <v>95</v>
+      </c>
+      <c r="E32" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" t="s">
+        <v>52</v>
+      </c>
+      <c r="C33" t="s">
+        <v>93</v>
+      </c>
+      <c r="D33" t="s">
+        <v>95</v>
+      </c>
+      <c r="E33" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>16</v>
+      </c>
+      <c r="B34" t="s">
+        <v>53</v>
+      </c>
+      <c r="C34" t="s">
+        <v>94</v>
+      </c>
+      <c r="D34" t="s">
+        <v>95</v>
+      </c>
+      <c r="E34" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>17</v>
+      </c>
+      <c r="B35" t="s">
+        <v>54</v>
+      </c>
+      <c r="C35" t="s">
+        <v>95</v>
+      </c>
+      <c r="D35" t="s">
+        <v>95</v>
+      </c>
+      <c r="E35" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" t="s">
+        <v>55</v>
+      </c>
+      <c r="C36" t="s">
+        <v>95</v>
+      </c>
+      <c r="D36" t="s">
+        <v>95</v>
+      </c>
+      <c r="E36" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>18</v>
+      </c>
+      <c r="B37" t="s">
+        <v>56</v>
+      </c>
+      <c r="C37" t="s">
+        <v>95</v>
+      </c>
+      <c r="D37" t="s">
+        <v>97</v>
+      </c>
+      <c r="E37" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>18</v>
+      </c>
+      <c r="B38" t="s">
+        <v>57</v>
+      </c>
+      <c r="C38" t="s">
+        <v>95</v>
+      </c>
+      <c r="D38" t="s">
+        <v>98</v>
+      </c>
+      <c r="E38" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>18</v>
+      </c>
+      <c r="B39" t="s">
+        <v>58</v>
+      </c>
+      <c r="C39" t="s">
+        <v>95</v>
+      </c>
+      <c r="D39" t="s">
+        <v>99</v>
+      </c>
+      <c r="E39" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>18</v>
+      </c>
+      <c r="B40" t="s">
+        <v>59</v>
+      </c>
+      <c r="C40" t="s">
+        <v>95</v>
+      </c>
+      <c r="D40" t="s">
+        <v>100</v>
+      </c>
+      <c r="E40" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>19</v>
+      </c>
+      <c r="B41" t="s">
         <v>60</v>
       </c>
-      <c r="D25" t="s">
+      <c r="C41" t="s">
+        <v>95</v>
+      </c>
+      <c r="D41" t="s">
+        <v>101</v>
+      </c>
+      <c r="E41" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>20</v>
+      </c>
+      <c r="B42" t="s">
         <v>61</v>
       </c>
-      <c r="E25" t="s">
-        <v>60</v>
+      <c r="C42" t="s">
+        <v>95</v>
+      </c>
+      <c r="D42" t="s">
+        <v>102</v>
+      </c>
+      <c r="E42" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>20</v>
+      </c>
+      <c r="B43" t="s">
+        <v>62</v>
+      </c>
+      <c r="C43" t="s">
+        <v>95</v>
+      </c>
+      <c r="D43" t="s">
+        <v>103</v>
+      </c>
+      <c r="E43" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
